--- a/basedatos_partidas/salida/descompuestos/CT-05-04-060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-04-060.xlsx
@@ -591,10 +591,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H12" t="n">
-        <v>8.75</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="13">
@@ -617,10 +617,10 @@
         <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>4.32</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="14">
@@ -643,10 +643,10 @@
         <v>1.08</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H14" t="n">
-        <v>4.54</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="15">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>40.52</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="20">
@@ -984,10 +984,10 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>46.75</v>
+        <v>46.21</v>
       </c>
       <c r="H31" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="32">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="5" t="n">
-        <v>47.22</v>
+        <v>46.67</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-05-04-060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-04-060.xlsx
@@ -695,10 +695,10 @@
         <v>0.6</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H16" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="17">
@@ -721,10 +721,10 @@
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H17" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>39.98</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="20">
@@ -984,7 +984,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>46.21</v>
+        <v>45.87</v>
       </c>
       <c r="H31" t="n">
         <v>0.46</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="5" t="n">
-        <v>46.67</v>
+        <v>46.33</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-05-04-060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-04-060.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 05 Estructuras</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Losas y entrepisos</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
